--- a/servers/maze_main_server/conf.d/data/doll_equip_pos_rank_v8【人偶-装备-部位排序】.xlsx
+++ b/servers/maze_main_server/conf.d/data/doll_equip_pos_rank_v8【人偶-装备-部位排序】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00669A47-9392-4E91-80FE-05B212580A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DF3AF6-2B73-40F9-B340-9A27DEDA914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -140,49 +140,32 @@
     <t>0:0</t>
   </si>
   <si>
+    <t>上衣</t>
+  </si>
+  <si>
+    <t>裤子</t>
+  </si>
+  <si>
+    <t>指环</t>
+  </si>
+  <si>
+    <t>挂饰</t>
+  </si>
+  <si>
     <t>默认解锁</t>
-  </si>
-  <si>
-    <t>帽子</t>
-  </si>
-  <si>
-    <t>9级解锁</t>
-  </si>
-  <si>
-    <t>上衣</t>
-  </si>
-  <si>
-    <t>14级解锁</t>
-  </si>
-  <si>
-    <t>裤子</t>
-  </si>
-  <si>
-    <t>18级解锁</t>
-  </si>
-  <si>
-    <t>指环</t>
-  </si>
-  <si>
-    <t>26级解锁</t>
-  </si>
-  <si>
-    <t>鞋子</t>
-  </si>
-  <si>
-    <t>30级解锁</t>
-  </si>
-  <si>
-    <t>护手</t>
-  </si>
-  <si>
-    <t>4级解锁</t>
-  </si>
-  <si>
-    <t>挂饰</t>
-  </si>
-  <si>
-    <t>22级解锁</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>头盔</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>靴子</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护腕</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -783,7 +766,7 @@
         <v>34</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
@@ -794,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>34</v>
@@ -809,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -818,7 +801,7 @@
         <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K6" s="1">
         <v>2</v>
@@ -829,7 +812,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>34</v>
@@ -844,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -864,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>34</v>
@@ -879,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -888,7 +871,7 @@
         <v>34</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K8" s="1">
         <v>5</v>
@@ -899,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>34</v>
@@ -914,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -923,7 +906,7 @@
         <v>34</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K9" s="1">
         <v>7</v>
@@ -934,7 +917,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>34</v>
@@ -949,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -958,7 +941,7 @@
         <v>34</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
@@ -969,7 +952,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>34</v>
@@ -984,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -993,7 +976,7 @@
         <v>34</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K11" s="1">
         <v>6</v>
@@ -1004,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>34</v>
@@ -1019,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -1028,7 +1011,7 @@
         <v>34</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="K12" s="1">
         <v>4</v>
